--- a/hypatia/examples/Planning_2Regions/config.xlsx
+++ b/hypatia/examples/Planning_2Regions/config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polimi365-my.sharepoint.com/personal/10530003_polimi_it/Documents/Documenti/GitHub/Hypatia-SESAM/hypatia/examples/Planning_teaching/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polimi365-my.sharepoint.com/personal/10394890_polimi_it/Documents/Research/Repositories/Hypatia-polimi/hypatia/examples/Planning_2Regions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_399507946124473CD69F2D2E2B28EDF8608B3BFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB66216F-E043-48E2-9099-9E0A9B5C0682}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_399507946124473CD69F2D2E2B28EDF8608B3BFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96874AFD-F8A3-4218-8E2E-04440B42B588}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Techs" sheetId="1" r:id="rId1"/>
@@ -948,6 +948,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
@@ -1214,15 +1217,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100241E96938535DD4B921FCDFB54345D30" ma:contentTypeVersion="16" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="ea9f1ad5a580c8ec0c54747f8c275290">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e" xmlns:ns3="e67e9a88-35e1-4b39-8da9-a609eb308282" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a21d2b210d3c14c0eb20b1c12c2a17c" ns2:_="" ns3:_="">
     <xsd:import namespace="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e"/>
@@ -1465,15 +1459,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24802015-4ADE-4956-97E7-F806D57E32A9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2AC6781-9D25-4D8C-9F2E-53294FC6CF02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1490,4 +1485,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24802015-4ADE-4956-97E7-F806D57E32A9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>